--- a/docentes/Moreno Aroyo Anél - Estadisticos 20222.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -76,18 +76,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>PALOMINO</t>
   </si>
   <si>
@@ -103,18 +94,9 @@
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -130,16 +112,7 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
     <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
   </si>
   <si>
     <t>AARON MIGUEL</t>
@@ -929,7 +902,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -961,22 +934,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920340</v>
+        <v>22330051920084</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -984,22 +957,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920084</v>
+        <v>22330051920043</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1007,16 +980,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920031</v>
+        <v>22330051920049</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1030,139 +1003,70 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920034</v>
+        <v>22330051920121</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920043</v>
+        <v>22330051920068</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920049</v>
+        <v>22330051920071</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920121</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920068</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920071</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20222.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -76,52 +76,16 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>TELE</t>
-  </si>
-  <si>
     <t>MACHORRO</t>
   </si>
   <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>BETSABETH</t>
   </si>
   <si>
     <t>JIMENA</t>
@@ -671,16 +635,19 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>97.67</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -717,16 +684,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>82.5</v>
+      </c>
+      <c r="H4">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -740,16 +710,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>89.19</v>
+      </c>
+      <c r="H5">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -805,16 +778,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>88.37</v>
+        <v>97.67</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -857,16 +830,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -883,16 +856,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>83.78</v>
+        <v>89.19</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -902,7 +875,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -934,16 +907,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920084</v>
+        <v>22330051920068</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -952,121 +925,29 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920043</v>
+        <v>22330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920049</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920121</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920068</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920071</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20222.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20222.xlsx
@@ -661,16 +661,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>94.87</v>
+      </c>
+      <c r="H3">
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -813,7 +816,7 @@
         <v>94.87</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20222.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20222.xlsx
@@ -928,7 +928,7 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -951,7 +951,7 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20222.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -82,16 +82,25 @@
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
     <t>JIMENA</t>
   </si>
   <si>
     <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
   </si>
 </sst>
 </file>
@@ -878,7 +887,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -916,10 +925,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -939,10 +948,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -951,6 +960,29 @@
         <v>11</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920049</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20222.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -76,13 +76,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>MACHORRO</t>
   </si>
   <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>VENTURA</t>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
   </si>
   <si>
     <t>ROMERO</t>
@@ -91,7 +109,22 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>SALOMON</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
   </si>
   <si>
     <t>JIMENA</t>
@@ -100,7 +133,19 @@
     <t>DANA PAOLA</t>
   </si>
   <si>
-    <t>DANIEL</t>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>ILEANA</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>CARLOS EDUARDO</t>
+  </si>
+  <si>
+    <t>JOSE RAUL</t>
   </si>
 </sst>
 </file>
@@ -790,16 +835,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>97.67</v>
+        <v>90.7</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -816,16 +861,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>94.87</v>
+        <v>84.62</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -842,16 +887,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>82.5</v>
+        <v>80</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -868,16 +913,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>89.19</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -887,7 +932,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -919,22 +964,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920068</v>
+        <v>22330051920157</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -942,16 +987,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920071</v>
+        <v>22330051920068</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -965,25 +1010,140 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920049</v>
+        <v>22330051920071</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920031</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920114</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920172</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920380</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920036</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20222.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -79,7 +79,7 @@
     <t>CERON</t>
   </si>
   <si>
-    <t>MACHORRO</t>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>MENDOZA</t>
@@ -91,9 +91,6 @@
     <t>RIVERA</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -103,7 +100,7 @@
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>ROMERO</t>
+    <t>ANGUIANO</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
@@ -115,9 +112,6 @@
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
@@ -127,7 +121,7 @@
     <t>JESUS EMMANUEL</t>
   </si>
   <si>
-    <t>JIMENA</t>
+    <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>DANA PAOLA</t>
@@ -137,9 +131,6 @@
   </si>
   <si>
     <t>ILEANA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>CARLOS EDUARDO</t>
@@ -932,7 +923,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -970,10 +961,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -987,22 +978,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920068</v>
+        <v>22330051920172</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1016,10 +1007,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1039,10 +1030,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1062,10 +1053,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1079,22 +1070,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920172</v>
+        <v>22330051920380</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1102,47 +1093,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920380</v>
+        <v>22330051920036</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920036</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>
